--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/before_conversion_yukon_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/before_conversion_yukon_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="120">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Yukon</t>
@@ -734,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD89"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -762,9 +765,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,13 +859,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>63.40501</v>
@@ -885,12 +892,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>59.4278</v>
@@ -926,12 +933,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>59.63029</v>
@@ -967,12 +974,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>60.38142</v>
@@ -1014,12 +1021,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>60.27582</v>
@@ -1061,12 +1068,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>60.00999</v>
@@ -1108,12 +1115,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>60.19948</v>
@@ -1155,12 +1162,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>61.42595</v>
@@ -1184,12 +1191,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>61.9415</v>
@@ -1213,12 +1220,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>61.7</v>
@@ -1242,12 +1249,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>62.343</v>
@@ -1259,12 +1266,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>62.817</v>
@@ -1288,12 +1295,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>64.011</v>
@@ -1329,12 +1336,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>61.25238</v>
@@ -1358,12 +1365,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>62.37167</v>
@@ -1389,10 +1396,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>62.82168</v>
@@ -1418,10 +1425,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18">
         <v>62.6638</v>
@@ -1447,10 +1454,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C19">
         <v>61.86137</v>
@@ -1488,10 +1495,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>63.28318</v>
@@ -1505,10 +1512,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C21">
         <v>61.95491</v>
@@ -1534,10 +1541,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22">
         <v>60.8789</v>
@@ -1581,10 +1588,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23">
         <v>60.76146</v>
@@ -1628,10 +1635,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C24">
         <v>60.75248</v>
@@ -1675,10 +1682,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25">
         <v>60.78902</v>
@@ -1722,10 +1729,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26">
         <v>60.78873</v>
@@ -1769,10 +1776,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27">
         <v>60.74632</v>
@@ -1810,10 +1817,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>63.06761</v>
@@ -1857,10 +1864,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C29">
         <v>63.70526</v>
@@ -1904,10 +1911,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C30">
         <v>60.90144</v>
@@ -1951,10 +1958,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>64.55104</v>
@@ -1998,10 +2005,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C32">
         <v>64.60932</v>
@@ -2045,10 +2052,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C33">
         <v>60.19873</v>
@@ -2092,10 +2099,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34">
         <v>60.19828</v>
@@ -2139,10 +2146,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C35">
         <v>60.15235</v>
@@ -2186,10 +2193,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C36">
         <v>61.66667</v>
@@ -2227,10 +2234,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C37">
         <v>57.40435</v>
@@ -2274,10 +2281,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C38">
         <v>57.01681</v>
@@ -2318,10 +2325,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C39">
         <v>57.71487</v>
@@ -2365,10 +2372,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C40">
         <v>57.77206</v>
@@ -2412,10 +2419,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41">
         <v>60.915894</v>
@@ -2459,10 +2466,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42">
         <v>59.98333</v>
@@ -2500,10 +2507,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C43">
         <v>59.96917</v>
@@ -2541,10 +2548,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C44">
         <v>55.9778245</v>
@@ -2558,10 +2565,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C45">
         <v>55.9299379</v>
@@ -2575,10 +2582,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C46">
         <v>55.865437</v>
@@ -2592,10 +2599,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C47">
         <v>56.2296634</v>
@@ -2609,10 +2616,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C48">
         <v>56.6755021</v>
@@ -2626,10 +2633,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C49">
         <v>61.95349</v>
@@ -2643,10 +2650,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B50" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C50">
         <v>62.115</v>
@@ -2672,10 +2679,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C51">
         <v>61.4103</v>
@@ -2713,10 +2720,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C52">
         <v>59.472</v>
@@ -2730,10 +2737,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C53">
         <v>64.14593000000001</v>
@@ -2771,10 +2778,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B54" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C54">
         <v>64.167</v>
@@ -2788,10 +2795,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C55">
         <v>64.009</v>
@@ -2829,10 +2836,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C56">
         <v>64.009</v>
@@ -2870,10 +2877,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C57">
         <v>64.08333</v>
@@ -2911,10 +2918,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B58" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C58">
         <v>59.96917</v>
@@ -2952,10 +2959,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C59">
         <v>59.87721</v>
@@ -2993,10 +3000,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C60">
         <v>59.40394</v>
@@ -3034,10 +3041,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C61">
         <v>59.27227</v>
@@ -3051,10 +3058,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B62" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C62">
         <v>59.64472</v>
@@ -3068,10 +3075,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C63">
         <v>59.50406</v>
@@ -3085,10 +3092,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64">
         <v>58.92503</v>
@@ -3102,10 +3109,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C65">
         <v>59.4963</v>
@@ -3119,10 +3126,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C66">
         <v>59.61295</v>
@@ -3136,10 +3143,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C67">
         <v>62.00365</v>
@@ -3174,10 +3181,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C68">
         <v>64.146</v>
@@ -3215,10 +3222,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C69">
         <v>65.0309834</v>
@@ -3232,10 +3239,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C70">
         <v>65.18466100000001</v>
@@ -3249,10 +3256,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C71">
         <v>65.48945399999999</v>
@@ -3266,10 +3273,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C72">
         <v>65.102092</v>
@@ -3283,10 +3290,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B73" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C73">
         <v>64.488981</v>
@@ -3300,10 +3307,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C74">
         <v>60.889151</v>
@@ -3317,10 +3324,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C75">
         <v>58.665373</v>
@@ -3334,10 +3341,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B76" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C76">
         <v>58.122279</v>
@@ -3351,10 +3358,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C77">
         <v>58.005582</v>
@@ -3368,10 +3375,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B78" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C78">
         <v>57.839992</v>
@@ -3385,10 +3392,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C79">
         <v>57.769868</v>
@@ -3402,10 +3409,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B80" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C80">
         <v>57.806075</v>
@@ -3419,10 +3426,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B81" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C81">
         <v>57.778095</v>
@@ -3436,10 +3443,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C82">
         <v>56.846531</v>
@@ -3453,10 +3460,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B83" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C83">
         <v>56.718592</v>
@@ -3470,10 +3477,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B84" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C84">
         <v>57.0896723</v>
@@ -3487,10 +3494,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B85" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C85">
         <v>56.726836</v>
@@ -3504,10 +3511,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C86">
         <v>56.6506976</v>
@@ -3521,10 +3528,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C87">
         <v>56.7088271</v>
@@ -3538,10 +3545,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C88">
         <v>56.4570945</v>
@@ -3555,10 +3562,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C89">
         <v>56.1482276</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/before_conversion_yukon_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/before_conversion_yukon_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="121">
   <si>
     <t>location</t>
   </si>
@@ -374,6 +374,9 @@
   </si>
   <si>
     <t>Unuk River HS</t>
+  </si>
+  <si>
+    <t>Granite</t>
   </si>
 </sst>
 </file>
@@ -876,6 +879,9 @@
       <c r="D2">
         <v>-125.9557</v>
       </c>
+      <c r="F2" t="s">
+        <v>120</v>
+      </c>
       <c r="N2">
         <v>49</v>
       </c>
@@ -905,6 +911,9 @@
       <c r="D3">
         <v>-126.09892</v>
       </c>
+      <c r="F3" t="s">
+        <v>120</v>
+      </c>
       <c r="J3">
         <v>6.5</v>
       </c>
@@ -946,6 +955,9 @@
       <c r="D4">
         <v>-126.90672</v>
       </c>
+      <c r="F4" t="s">
+        <v>120</v>
+      </c>
       <c r="N4">
         <v>41</v>
       </c>
@@ -987,6 +999,9 @@
       <c r="D5">
         <v>-125.56873</v>
       </c>
+      <c r="F5" t="s">
+        <v>120</v>
+      </c>
       <c r="I5">
         <v>667</v>
       </c>
@@ -1034,6 +1049,9 @@
       <c r="D6">
         <v>-125.64786</v>
       </c>
+      <c r="F6" t="s">
+        <v>120</v>
+      </c>
       <c r="I6">
         <v>423</v>
       </c>
@@ -1081,6 +1099,9 @@
       <c r="D7">
         <v>-125.74744</v>
       </c>
+      <c r="F7" t="s">
+        <v>120</v>
+      </c>
       <c r="I7">
         <v>488</v>
       </c>
@@ -1128,6 +1149,9 @@
       <c r="D8">
         <v>-125.78986</v>
       </c>
+      <c r="F8" t="s">
+        <v>120</v>
+      </c>
       <c r="I8">
         <v>367</v>
       </c>
@@ -1175,6 +1199,9 @@
       <c r="D9">
         <v>-126.57484</v>
       </c>
+      <c r="F9" t="s">
+        <v>120</v>
+      </c>
       <c r="N9">
         <v>1.4</v>
       </c>
@@ -1204,6 +1231,9 @@
       <c r="D10">
         <v>-127.17908</v>
       </c>
+      <c r="F10" t="s">
+        <v>120</v>
+      </c>
       <c r="N10">
         <v>3.9</v>
       </c>
@@ -1233,6 +1263,9 @@
       <c r="D11">
         <v>-127.283</v>
       </c>
+      <c r="F11" t="s">
+        <v>120</v>
+      </c>
       <c r="N11">
         <v>28</v>
       </c>
@@ -1262,6 +1295,9 @@
       <c r="D12">
         <v>-128.1591</v>
       </c>
+      <c r="F12" t="s">
+        <v>120</v>
+      </c>
       <c r="AD12">
         <v>7</v>
       </c>
@@ -1279,6 +1315,9 @@
       <c r="D13">
         <v>-128.833</v>
       </c>
+      <c r="F13" t="s">
+        <v>120</v>
+      </c>
       <c r="N13">
         <v>56</v>
       </c>
@@ -1308,6 +1347,9 @@
       <c r="D14">
         <v>-129.00361</v>
       </c>
+      <c r="F14" t="s">
+        <v>120</v>
+      </c>
       <c r="J14">
         <v>7.88</v>
       </c>
@@ -1349,6 +1391,9 @@
       <c r="D15">
         <v>-124.05754</v>
       </c>
+      <c r="F15" t="s">
+        <v>120</v>
+      </c>
       <c r="Q15">
         <v>2277</v>
       </c>
@@ -1378,6 +1423,9 @@
       <c r="D16">
         <v>-128.67981</v>
       </c>
+      <c r="F16" t="s">
+        <v>120</v>
+      </c>
       <c r="N16">
         <v>67</v>
       </c>
@@ -1407,6 +1455,9 @@
       <c r="D17">
         <v>-128.1336</v>
       </c>
+      <c r="F17" t="s">
+        <v>120</v>
+      </c>
       <c r="N17">
         <v>50.2</v>
       </c>
@@ -1436,6 +1487,9 @@
       <c r="D18">
         <v>-127.91881</v>
       </c>
+      <c r="F18" t="s">
+        <v>120</v>
+      </c>
       <c r="N18">
         <v>22</v>
       </c>
@@ -1465,6 +1519,9 @@
       <c r="D19">
         <v>-129.66929</v>
       </c>
+      <c r="F19" t="s">
+        <v>120</v>
+      </c>
       <c r="J19">
         <v>7.3</v>
       </c>
@@ -1506,6 +1563,9 @@
       <c r="D20">
         <v>-130.22964</v>
       </c>
+      <c r="F20" t="s">
+        <v>120</v>
+      </c>
       <c r="AD20">
         <v>7</v>
       </c>
@@ -1523,6 +1583,9 @@
       <c r="D21">
         <v>-128.20613</v>
       </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
       <c r="N21">
         <v>47</v>
       </c>
@@ -1552,6 +1615,9 @@
       <c r="D22">
         <v>-135.36011</v>
       </c>
+      <c r="F22" t="s">
+        <v>120</v>
+      </c>
       <c r="I22">
         <v>2905</v>
       </c>
@@ -1599,6 +1665,9 @@
       <c r="D23">
         <v>-135.14582</v>
       </c>
+      <c r="F23" t="s">
+        <v>120</v>
+      </c>
       <c r="I23">
         <v>336</v>
       </c>
@@ -1646,6 +1715,9 @@
       <c r="D24">
         <v>-135.128</v>
       </c>
+      <c r="F24" t="s">
+        <v>120</v>
+      </c>
       <c r="I24">
         <v>347</v>
       </c>
@@ -1693,6 +1765,9 @@
       <c r="D25">
         <v>-135.20278</v>
       </c>
+      <c r="F25" t="s">
+        <v>120</v>
+      </c>
       <c r="I25">
         <v>360</v>
       </c>
@@ -1740,6 +1815,9 @@
       <c r="D26">
         <v>-135.20118</v>
       </c>
+      <c r="F26" t="s">
+        <v>120</v>
+      </c>
       <c r="I26">
         <v>404</v>
       </c>
@@ -1787,6 +1865,9 @@
       <c r="D27">
         <v>-135.10815</v>
       </c>
+      <c r="F27" t="s">
+        <v>120</v>
+      </c>
       <c r="N27">
         <v>2.9</v>
       </c>
@@ -1828,6 +1909,9 @@
       <c r="D28">
         <v>-135.71165</v>
       </c>
+      <c r="F28" t="s">
+        <v>120</v>
+      </c>
       <c r="I28">
         <v>268</v>
       </c>
@@ -1875,6 +1959,9 @@
       <c r="D29">
         <v>-137.31082</v>
       </c>
+      <c r="F29" t="s">
+        <v>120</v>
+      </c>
       <c r="I29">
         <v>441</v>
       </c>
@@ -1922,6 +2009,9 @@
       <c r="D30">
         <v>-137.96969</v>
       </c>
+      <c r="F30" t="s">
+        <v>120</v>
+      </c>
       <c r="I30">
         <v>660</v>
       </c>
@@ -1969,6 +2059,9 @@
       <c r="D31">
         <v>-134.70978</v>
       </c>
+      <c r="F31" t="s">
+        <v>120</v>
+      </c>
       <c r="I31">
         <v>390</v>
       </c>
@@ -2016,6 +2109,9 @@
       <c r="D32">
         <v>-135.00865</v>
       </c>
+      <c r="F32" t="s">
+        <v>120</v>
+      </c>
       <c r="I32">
         <v>207</v>
       </c>
@@ -2063,6 +2159,9 @@
       <c r="D33">
         <v>-125.51287</v>
       </c>
+      <c r="F33" t="s">
+        <v>120</v>
+      </c>
       <c r="I33">
         <v>554</v>
       </c>
@@ -2110,6 +2209,9 @@
       <c r="D34">
         <v>-125.52384</v>
       </c>
+      <c r="F34" t="s">
+        <v>120</v>
+      </c>
       <c r="I34">
         <v>538</v>
       </c>
@@ -2157,6 +2259,9 @@
       <c r="D35">
         <v>-127.43579</v>
       </c>
+      <c r="F35" t="s">
+        <v>120</v>
+      </c>
       <c r="I35">
         <v>531</v>
       </c>
@@ -2204,6 +2309,9 @@
       <c r="D36">
         <v>-127.58333</v>
       </c>
+      <c r="F36" t="s">
+        <v>120</v>
+      </c>
       <c r="J36">
         <v>7.06</v>
       </c>
@@ -2245,6 +2353,9 @@
       <c r="D37">
         <v>-130.91825</v>
       </c>
+      <c r="F37" t="s">
+        <v>120</v>
+      </c>
       <c r="I37">
         <v>2400</v>
       </c>
@@ -2292,6 +2403,9 @@
       <c r="D38">
         <v>-131.30861</v>
       </c>
+      <c r="F38" t="s">
+        <v>120</v>
+      </c>
       <c r="J38">
         <v>6.59</v>
       </c>
@@ -2336,6 +2450,9 @@
       <c r="D39">
         <v>-130.70947</v>
       </c>
+      <c r="F39" t="s">
+        <v>120</v>
+      </c>
       <c r="I39">
         <v>3000</v>
       </c>
@@ -2383,6 +2500,9 @@
       <c r="D40">
         <v>-130.74563</v>
       </c>
+      <c r="F40" t="s">
+        <v>120</v>
+      </c>
       <c r="I40">
         <v>2780</v>
       </c>
@@ -2430,6 +2550,9 @@
       <c r="D41">
         <v>-135.18883</v>
       </c>
+      <c r="F41" t="s">
+        <v>120</v>
+      </c>
       <c r="I41">
         <v>624</v>
       </c>
@@ -2477,6 +2600,9 @@
       <c r="D42">
         <v>-134.21667</v>
       </c>
+      <c r="F42" t="s">
+        <v>120</v>
+      </c>
       <c r="J42">
         <v>7.53</v>
       </c>
@@ -2518,6 +2644,9 @@
       <c r="D43">
         <v>-134.22623</v>
       </c>
+      <c r="F43" t="s">
+        <v>120</v>
+      </c>
       <c r="J43">
         <v>7.29</v>
       </c>
@@ -2559,6 +2688,9 @@
       <c r="D44">
         <v>-131.6640596</v>
       </c>
+      <c r="F44" t="s">
+        <v>120</v>
+      </c>
       <c r="AD44">
         <v>7</v>
       </c>
@@ -2576,6 +2708,9 @@
       <c r="D45">
         <v>-131.568339</v>
       </c>
+      <c r="F45" t="s">
+        <v>120</v>
+      </c>
       <c r="AD45">
         <v>7</v>
       </c>
@@ -2593,6 +2728,9 @@
       <c r="D46">
         <v>-131.0605</v>
       </c>
+      <c r="F46" t="s">
+        <v>120</v>
+      </c>
       <c r="AD46">
         <v>7</v>
       </c>
@@ -2610,6 +2748,9 @@
       <c r="D47">
         <v>-131.4570819</v>
       </c>
+      <c r="F47" t="s">
+        <v>120</v>
+      </c>
       <c r="AD47">
         <v>7</v>
       </c>
@@ -2627,6 +2768,9 @@
       <c r="D48">
         <v>131.8932711</v>
       </c>
+      <c r="F48" t="s">
+        <v>120</v>
+      </c>
       <c r="AD48">
         <v>7</v>
       </c>
@@ -2644,6 +2788,9 @@
       <c r="D49">
         <v>-128.20347</v>
       </c>
+      <c r="F49" t="s">
+        <v>120</v>
+      </c>
       <c r="AD49">
         <v>7</v>
       </c>
@@ -2661,6 +2808,9 @@
       <c r="D50">
         <v>-128.405</v>
       </c>
+      <c r="F50" t="s">
+        <v>120</v>
+      </c>
       <c r="N50">
         <v>0.8</v>
       </c>
@@ -2690,6 +2840,9 @@
       <c r="D51">
         <v>-127.88</v>
       </c>
+      <c r="F51" t="s">
+        <v>120</v>
+      </c>
       <c r="J51">
         <v>7.4</v>
       </c>
@@ -2731,6 +2884,9 @@
       <c r="D52">
         <v>-137.715</v>
       </c>
+      <c r="F52" t="s">
+        <v>120</v>
+      </c>
       <c r="AD52">
         <v>7</v>
       </c>
@@ -2748,6 +2904,9 @@
       <c r="D53">
         <v>-128.45046</v>
       </c>
+      <c r="F53" t="s">
+        <v>120</v>
+      </c>
       <c r="J53">
         <v>7.4</v>
       </c>
@@ -2789,6 +2948,9 @@
       <c r="D54">
         <v>-128.25</v>
       </c>
+      <c r="F54" t="s">
+        <v>120</v>
+      </c>
       <c r="AD54">
         <v>7</v>
       </c>
@@ -2806,6 +2968,9 @@
       <c r="D55">
         <v>-129.00417</v>
       </c>
+      <c r="F55" t="s">
+        <v>120</v>
+      </c>
       <c r="J55">
         <v>7.9</v>
       </c>
@@ -2847,6 +3012,9 @@
       <c r="D56">
         <v>-129.00861</v>
       </c>
+      <c r="F56" t="s">
+        <v>120</v>
+      </c>
       <c r="J56">
         <v>7.87</v>
       </c>
@@ -2888,6 +3056,9 @@
       <c r="D57">
         <v>-128.41667</v>
       </c>
+      <c r="F57" t="s">
+        <v>120</v>
+      </c>
       <c r="J57">
         <v>7.5</v>
       </c>
@@ -2929,6 +3100,9 @@
       <c r="D58">
         <v>-134.22623</v>
       </c>
+      <c r="F58" t="s">
+        <v>120</v>
+      </c>
       <c r="J58">
         <v>8.199999999999999</v>
       </c>
@@ -2970,6 +3144,9 @@
       <c r="D59">
         <v>-133.98356</v>
       </c>
+      <c r="F59" t="s">
+        <v>120</v>
+      </c>
       <c r="J59">
         <v>7.6</v>
       </c>
@@ -3011,6 +3188,9 @@
       <c r="D60">
         <v>-133.57545</v>
       </c>
+      <c r="F60" t="s">
+        <v>120</v>
+      </c>
       <c r="J60">
         <v>8.199999999999999</v>
       </c>
@@ -3052,6 +3232,9 @@
       <c r="D61">
         <v>-132.62351</v>
       </c>
+      <c r="F61" t="s">
+        <v>120</v>
+      </c>
       <c r="AD61">
         <v>7</v>
       </c>
@@ -3069,6 +3252,9 @@
       <c r="D62">
         <v>-129.73254</v>
       </c>
+      <c r="F62" t="s">
+        <v>120</v>
+      </c>
       <c r="AD62">
         <v>7</v>
       </c>
@@ -3086,6 +3272,9 @@
       <c r="D63">
         <v>-125.95633</v>
       </c>
+      <c r="F63" t="s">
+        <v>120</v>
+      </c>
       <c r="AD63">
         <v>7</v>
       </c>
@@ -3103,6 +3292,9 @@
       <c r="D64">
         <v>-125.07669</v>
       </c>
+      <c r="F64" t="s">
+        <v>120</v>
+      </c>
       <c r="AD64">
         <v>7</v>
       </c>
@@ -3120,6 +3312,9 @@
       <c r="D65">
         <v>-124.85186</v>
       </c>
+      <c r="F65" t="s">
+        <v>120</v>
+      </c>
       <c r="AD65">
         <v>7</v>
       </c>
@@ -3137,6 +3332,9 @@
       <c r="D66">
         <v>-125.55107</v>
       </c>
+      <c r="F66" t="s">
+        <v>120</v>
+      </c>
       <c r="AD66">
         <v>7</v>
       </c>
@@ -3154,6 +3352,9 @@
       <c r="D67">
         <v>-127.02467</v>
       </c>
+      <c r="F67" t="s">
+        <v>120</v>
+      </c>
       <c r="J67">
         <v>6.4</v>
       </c>
@@ -3192,6 +3393,9 @@
       <c r="D68">
         <v>-128.432</v>
       </c>
+      <c r="F68" t="s">
+        <v>120</v>
+      </c>
       <c r="J68">
         <v>7.3</v>
       </c>
@@ -3233,6 +3437,9 @@
       <c r="D69">
         <v>-146.0524335</v>
       </c>
+      <c r="F69" t="s">
+        <v>120</v>
+      </c>
       <c r="AD69">
         <v>7</v>
       </c>
@@ -3250,6 +3457,9 @@
       <c r="D70">
         <v>-144.692004</v>
       </c>
+      <c r="F70" t="s">
+        <v>120</v>
+      </c>
       <c r="AD70">
         <v>7</v>
       </c>
@@ -3267,6 +3477,9 @@
       <c r="D71">
         <v>-144.622314</v>
       </c>
+      <c r="F71" t="s">
+        <v>120</v>
+      </c>
       <c r="AD71">
         <v>7</v>
       </c>
@@ -3284,6 +3497,9 @@
       <c r="D72">
         <v>-142.732627</v>
       </c>
+      <c r="F72" t="s">
+        <v>120</v>
+      </c>
       <c r="AD72">
         <v>7</v>
       </c>
@@ -3301,6 +3517,9 @@
       <c r="D73">
         <v>-143.081535</v>
       </c>
+      <c r="F73" t="s">
+        <v>120</v>
+      </c>
       <c r="AD73">
         <v>7</v>
       </c>
@@ -3318,6 +3537,9 @@
       <c r="D74">
         <v>-142.289668</v>
       </c>
+      <c r="F74" t="s">
+        <v>120</v>
+      </c>
       <c r="AD74">
         <v>7</v>
       </c>
@@ -3335,6 +3557,9 @@
       <c r="D75">
         <v>-137.488566</v>
       </c>
+      <c r="F75" t="s">
+        <v>120</v>
+      </c>
       <c r="AD75">
         <v>7</v>
       </c>
@@ -3352,6 +3577,9 @@
       <c r="D76">
         <v>-135.892103</v>
       </c>
+      <c r="F76" t="s">
+        <v>120</v>
+      </c>
       <c r="AD76">
         <v>7</v>
       </c>
@@ -3369,6 +3597,9 @@
       <c r="D77">
         <v>-135.926934</v>
       </c>
+      <c r="F77" t="s">
+        <v>120</v>
+      </c>
       <c r="AD77">
         <v>7</v>
       </c>
@@ -3386,6 +3617,9 @@
       <c r="D78">
         <v>-136.035412</v>
       </c>
+      <c r="F78" t="s">
+        <v>120</v>
+      </c>
       <c r="AD78">
         <v>7</v>
       </c>
@@ -3403,6 +3637,9 @@
       <c r="D79">
         <v>-135.845988</v>
       </c>
+      <c r="F79" t="s">
+        <v>120</v>
+      </c>
       <c r="AD79">
         <v>7</v>
       </c>
@@ -3420,6 +3657,9 @@
       <c r="D80">
         <v>-136.338884</v>
       </c>
+      <c r="F80" t="s">
+        <v>120</v>
+      </c>
       <c r="AD80">
         <v>7</v>
       </c>
@@ -3437,6 +3677,9 @@
       <c r="D81">
         <v>-135.219618</v>
       </c>
+      <c r="F81" t="s">
+        <v>120</v>
+      </c>
       <c r="AD81">
         <v>7</v>
       </c>
@@ -3454,6 +3697,9 @@
       <c r="D82">
         <v>-135.379772</v>
       </c>
+      <c r="F82" t="s">
+        <v>120</v>
+      </c>
       <c r="AD82">
         <v>7</v>
       </c>
@@ -3471,6 +3717,9 @@
       <c r="D83">
         <v>-134.714728</v>
       </c>
+      <c r="F83" t="s">
+        <v>120</v>
+      </c>
       <c r="AD83">
         <v>7</v>
       </c>
@@ -3488,6 +3737,9 @@
       <c r="D84">
         <v>-134.8305897</v>
       </c>
+      <c r="F84" t="s">
+        <v>120</v>
+      </c>
       <c r="AD84">
         <v>7</v>
       </c>
@@ -3505,6 +3757,9 @@
       <c r="D85">
         <v>-132.05231</v>
       </c>
+      <c r="F85" t="s">
+        <v>120</v>
+      </c>
       <c r="AD85">
         <v>7</v>
       </c>
@@ -3522,6 +3777,9 @@
       <c r="D86">
         <v>-132.2534895</v>
       </c>
+      <c r="F86" t="s">
+        <v>120</v>
+      </c>
       <c r="AD86">
         <v>7</v>
       </c>
@@ -3539,6 +3797,9 @@
       <c r="D87">
         <v>-132.1978004</v>
       </c>
+      <c r="F87" t="s">
+        <v>120</v>
+      </c>
       <c r="AD87">
         <v>7</v>
       </c>
@@ -3556,6 +3817,9 @@
       <c r="D88">
         <v>-132.6023179</v>
       </c>
+      <c r="F88" t="s">
+        <v>120</v>
+      </c>
       <c r="AD88">
         <v>7</v>
       </c>
@@ -3572,6 +3836,9 @@
       </c>
       <c r="D89">
         <v>-130.9767313</v>
+      </c>
+      <c r="F89" t="s">
+        <v>120</v>
       </c>
       <c r="AD89">
         <v>7</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/before_conversion_yukon_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/YUKON_Datenbank/before_conversion_yukon_mapped_readable.xlsx
@@ -882,6 +882,9 @@
       <c r="F2" t="s">
         <v>120</v>
       </c>
+      <c r="H2">
+        <v>54</v>
+      </c>
       <c r="N2">
         <v>49</v>
       </c>
@@ -914,6 +917,9 @@
       <c r="F3" t="s">
         <v>120</v>
       </c>
+      <c r="H3">
+        <v>52</v>
+      </c>
       <c r="J3">
         <v>6.5</v>
       </c>
@@ -958,6 +964,9 @@
       <c r="F4" t="s">
         <v>120</v>
       </c>
+      <c r="H4">
+        <v>48</v>
+      </c>
       <c r="N4">
         <v>41</v>
       </c>
@@ -1002,6 +1011,9 @@
       <c r="F5" t="s">
         <v>120</v>
       </c>
+      <c r="H5">
+        <v>54.5</v>
+      </c>
       <c r="I5">
         <v>667</v>
       </c>
@@ -1052,6 +1064,9 @@
       <c r="F6" t="s">
         <v>120</v>
       </c>
+      <c r="H6">
+        <v>15</v>
+      </c>
       <c r="I6">
         <v>423</v>
       </c>
@@ -1102,6 +1117,9 @@
       <c r="F7" t="s">
         <v>120</v>
       </c>
+      <c r="H7">
+        <v>25.3</v>
+      </c>
       <c r="I7">
         <v>488</v>
       </c>
@@ -1152,6 +1170,9 @@
       <c r="F8" t="s">
         <v>120</v>
       </c>
+      <c r="H8">
+        <v>29.2</v>
+      </c>
       <c r="I8">
         <v>367</v>
       </c>
@@ -1202,6 +1223,9 @@
       <c r="F9" t="s">
         <v>120</v>
       </c>
+      <c r="H9">
+        <v>29</v>
+      </c>
       <c r="N9">
         <v>1.4</v>
       </c>
@@ -1234,6 +1258,9 @@
       <c r="F10" t="s">
         <v>120</v>
       </c>
+      <c r="H10">
+        <v>21</v>
+      </c>
       <c r="N10">
         <v>3.9</v>
       </c>
@@ -1266,6 +1293,9 @@
       <c r="F11" t="s">
         <v>120</v>
       </c>
+      <c r="H11">
+        <v>47</v>
+      </c>
       <c r="N11">
         <v>28</v>
       </c>
@@ -1298,6 +1328,9 @@
       <c r="F12" t="s">
         <v>120</v>
       </c>
+      <c r="H12">
+        <v>40</v>
+      </c>
       <c r="AD12">
         <v>7</v>
       </c>
@@ -1318,6 +1351,9 @@
       <c r="F13" t="s">
         <v>120</v>
       </c>
+      <c r="H13">
+        <v>64</v>
+      </c>
       <c r="N13">
         <v>56</v>
       </c>
@@ -1350,6 +1386,9 @@
       <c r="F14" t="s">
         <v>120</v>
       </c>
+      <c r="H14">
+        <v>8.5</v>
+      </c>
       <c r="J14">
         <v>7.88</v>
       </c>
@@ -1394,6 +1433,9 @@
       <c r="F15" t="s">
         <v>120</v>
       </c>
+      <c r="H15">
+        <v>37</v>
+      </c>
       <c r="Q15">
         <v>2277</v>
       </c>
@@ -1426,6 +1468,9 @@
       <c r="F16" t="s">
         <v>120</v>
       </c>
+      <c r="H16">
+        <v>58</v>
+      </c>
       <c r="N16">
         <v>67</v>
       </c>
@@ -1458,6 +1503,9 @@
       <c r="F17" t="s">
         <v>120</v>
       </c>
+      <c r="H17">
+        <v>45</v>
+      </c>
       <c r="N17">
         <v>50.2</v>
       </c>
@@ -1490,6 +1538,9 @@
       <c r="F18" t="s">
         <v>120</v>
       </c>
+      <c r="H18">
+        <v>44</v>
+      </c>
       <c r="N18">
         <v>22</v>
       </c>
@@ -1522,6 +1573,9 @@
       <c r="F19" t="s">
         <v>120</v>
       </c>
+      <c r="H19">
+        <v>16</v>
+      </c>
       <c r="J19">
         <v>7.3</v>
       </c>
@@ -1566,6 +1620,9 @@
       <c r="F20" t="s">
         <v>120</v>
       </c>
+      <c r="H20">
+        <v>33</v>
+      </c>
       <c r="AD20">
         <v>7</v>
       </c>
@@ -1586,6 +1643,9 @@
       <c r="F21" t="s">
         <v>120</v>
       </c>
+      <c r="H21">
+        <v>41</v>
+      </c>
       <c r="N21">
         <v>47</v>
       </c>
@@ -1618,6 +1678,9 @@
       <c r="F22" t="s">
         <v>120</v>
       </c>
+      <c r="H22">
+        <v>47</v>
+      </c>
       <c r="I22">
         <v>2905</v>
       </c>
@@ -1668,6 +1731,9 @@
       <c r="F23" t="s">
         <v>120</v>
       </c>
+      <c r="H23">
+        <v>12.7</v>
+      </c>
       <c r="I23">
         <v>336</v>
       </c>
@@ -1718,6 +1784,9 @@
       <c r="F24" t="s">
         <v>120</v>
       </c>
+      <c r="H24">
+        <v>18.5</v>
+      </c>
       <c r="I24">
         <v>347</v>
       </c>
@@ -1768,6 +1837,9 @@
       <c r="F25" t="s">
         <v>120</v>
       </c>
+      <c r="H25">
+        <v>15.8</v>
+      </c>
       <c r="I25">
         <v>360</v>
       </c>
@@ -1818,6 +1890,9 @@
       <c r="F26" t="s">
         <v>120</v>
       </c>
+      <c r="H26">
+        <v>12</v>
+      </c>
       <c r="I26">
         <v>404</v>
       </c>
@@ -1912,6 +1987,9 @@
       <c r="F28" t="s">
         <v>120</v>
       </c>
+      <c r="H28">
+        <v>54.5</v>
+      </c>
       <c r="I28">
         <v>268</v>
       </c>
@@ -1962,6 +2040,9 @@
       <c r="F29" t="s">
         <v>120</v>
       </c>
+      <c r="H29">
+        <v>25.1</v>
+      </c>
       <c r="I29">
         <v>441</v>
       </c>
@@ -2012,6 +2093,9 @@
       <c r="F30" t="s">
         <v>120</v>
       </c>
+      <c r="H30">
+        <v>17.7</v>
+      </c>
       <c r="I30">
         <v>660</v>
       </c>
@@ -2062,6 +2146,9 @@
       <c r="F31" t="s">
         <v>120</v>
       </c>
+      <c r="H31">
+        <v>45.6</v>
+      </c>
       <c r="I31">
         <v>390</v>
       </c>
@@ -2112,6 +2199,9 @@
       <c r="F32" t="s">
         <v>120</v>
       </c>
+      <c r="H32">
+        <v>10.2</v>
+      </c>
       <c r="I32">
         <v>207</v>
       </c>
@@ -2162,6 +2252,9 @@
       <c r="F33" t="s">
         <v>120</v>
       </c>
+      <c r="H33">
+        <v>53</v>
+      </c>
       <c r="I33">
         <v>554</v>
       </c>
@@ -2212,6 +2305,9 @@
       <c r="F34" t="s">
         <v>120</v>
       </c>
+      <c r="H34">
+        <v>43</v>
+      </c>
       <c r="I34">
         <v>538</v>
       </c>
@@ -2262,6 +2358,9 @@
       <c r="F35" t="s">
         <v>120</v>
       </c>
+      <c r="H35">
+        <v>13.2</v>
+      </c>
       <c r="I35">
         <v>531</v>
       </c>
@@ -2312,6 +2411,9 @@
       <c r="F36" t="s">
         <v>120</v>
       </c>
+      <c r="H36">
+        <v>11</v>
+      </c>
       <c r="J36">
         <v>7.06</v>
       </c>
@@ -2356,6 +2458,9 @@
       <c r="F37" t="s">
         <v>120</v>
       </c>
+      <c r="H37">
+        <v>42.5</v>
+      </c>
       <c r="I37">
         <v>2400</v>
       </c>
@@ -2406,6 +2511,9 @@
       <c r="F38" t="s">
         <v>120</v>
       </c>
+      <c r="H38">
+        <v>48.5</v>
+      </c>
       <c r="J38">
         <v>6.59</v>
       </c>
@@ -2453,6 +2561,9 @@
       <c r="F39" t="s">
         <v>120</v>
       </c>
+      <c r="H39">
+        <v>46</v>
+      </c>
       <c r="I39">
         <v>3000</v>
       </c>
@@ -2503,6 +2614,9 @@
       <c r="F40" t="s">
         <v>120</v>
       </c>
+      <c r="H40">
+        <v>36</v>
+      </c>
       <c r="I40">
         <v>2780</v>
       </c>
@@ -2553,6 +2667,9 @@
       <c r="F41" t="s">
         <v>120</v>
       </c>
+      <c r="H41">
+        <v>13.7</v>
+      </c>
       <c r="I41">
         <v>624</v>
       </c>
@@ -2603,6 +2720,9 @@
       <c r="F42" t="s">
         <v>120</v>
       </c>
+      <c r="H42">
+        <v>9.5</v>
+      </c>
       <c r="J42">
         <v>7.53</v>
       </c>
@@ -2647,6 +2767,9 @@
       <c r="F43" t="s">
         <v>120</v>
       </c>
+      <c r="H43">
+        <v>15</v>
+      </c>
       <c r="J43">
         <v>7.29</v>
       </c>
@@ -2691,6 +2814,9 @@
       <c r="F44" t="s">
         <v>120</v>
       </c>
+      <c r="H44">
+        <v>88.3</v>
+      </c>
       <c r="AD44">
         <v>7</v>
       </c>
@@ -2711,6 +2837,9 @@
       <c r="F45" t="s">
         <v>120</v>
       </c>
+      <c r="H45">
+        <v>74</v>
+      </c>
       <c r="AD45">
         <v>7</v>
       </c>
@@ -2751,6 +2880,9 @@
       <c r="F47" t="s">
         <v>120</v>
       </c>
+      <c r="H47">
+        <v>57</v>
+      </c>
       <c r="AD47">
         <v>7</v>
       </c>
@@ -2771,6 +2903,9 @@
       <c r="F48" t="s">
         <v>120</v>
       </c>
+      <c r="H48">
+        <v>26</v>
+      </c>
       <c r="AD48">
         <v>7</v>
       </c>
@@ -2791,6 +2926,9 @@
       <c r="F49" t="s">
         <v>120</v>
       </c>
+      <c r="H49">
+        <v>29</v>
+      </c>
       <c r="AD49">
         <v>7</v>
       </c>
@@ -2811,6 +2949,9 @@
       <c r="F50" t="s">
         <v>120</v>
       </c>
+      <c r="H50">
+        <v>32</v>
+      </c>
       <c r="N50">
         <v>0.8</v>
       </c>
@@ -2843,6 +2984,9 @@
       <c r="F51" t="s">
         <v>120</v>
       </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
       <c r="J51">
         <v>7.4</v>
       </c>
@@ -2907,6 +3051,9 @@
       <c r="F53" t="s">
         <v>120</v>
       </c>
+      <c r="H53">
+        <v>16</v>
+      </c>
       <c r="J53">
         <v>7.4</v>
       </c>
@@ -2971,6 +3118,9 @@
       <c r="F55" t="s">
         <v>120</v>
       </c>
+      <c r="H55">
+        <v>10</v>
+      </c>
       <c r="J55">
         <v>7.9</v>
       </c>
@@ -3015,6 +3165,9 @@
       <c r="F56" t="s">
         <v>120</v>
       </c>
+      <c r="H56">
+        <v>10</v>
+      </c>
       <c r="J56">
         <v>7.87</v>
       </c>
@@ -3059,6 +3212,9 @@
       <c r="F57" t="s">
         <v>120</v>
       </c>
+      <c r="H57">
+        <v>46</v>
+      </c>
       <c r="J57">
         <v>7.5</v>
       </c>
@@ -3103,6 +3259,9 @@
       <c r="F58" t="s">
         <v>120</v>
       </c>
+      <c r="H58">
+        <v>17</v>
+      </c>
       <c r="J58">
         <v>8.199999999999999</v>
       </c>
@@ -3147,6 +3306,9 @@
       <c r="F59" t="s">
         <v>120</v>
       </c>
+      <c r="H59">
+        <v>13</v>
+      </c>
       <c r="J59">
         <v>7.6</v>
       </c>
@@ -3191,6 +3353,9 @@
       <c r="F60" t="s">
         <v>120</v>
       </c>
+      <c r="H60">
+        <v>29</v>
+      </c>
       <c r="J60">
         <v>8.199999999999999</v>
       </c>
@@ -3275,6 +3440,9 @@
       <c r="F63" t="s">
         <v>120</v>
       </c>
+      <c r="H63">
+        <v>42</v>
+      </c>
       <c r="AD63">
         <v>7</v>
       </c>
@@ -3335,6 +3503,9 @@
       <c r="F66" t="s">
         <v>120</v>
       </c>
+      <c r="H66">
+        <v>58</v>
+      </c>
       <c r="AD66">
         <v>7</v>
       </c>
@@ -3355,6 +3526,9 @@
       <c r="F67" t="s">
         <v>120</v>
       </c>
+      <c r="H67">
+        <v>3</v>
+      </c>
       <c r="J67">
         <v>6.4</v>
       </c>
@@ -3396,6 +3570,9 @@
       <c r="F68" t="s">
         <v>120</v>
       </c>
+      <c r="H68">
+        <v>22</v>
+      </c>
       <c r="J68">
         <v>7.3</v>
       </c>
@@ -3440,6 +3617,9 @@
       <c r="F69" t="s">
         <v>120</v>
       </c>
+      <c r="H69">
+        <v>74</v>
+      </c>
       <c r="AD69">
         <v>7</v>
       </c>
@@ -3460,6 +3640,9 @@
       <c r="F70" t="s">
         <v>120</v>
       </c>
+      <c r="H70">
+        <v>61</v>
+      </c>
       <c r="AD70">
         <v>7</v>
       </c>
@@ -3480,6 +3663,9 @@
       <c r="F71" t="s">
         <v>120</v>
       </c>
+      <c r="H71">
+        <v>57.2</v>
+      </c>
       <c r="AD71">
         <v>7</v>
       </c>
@@ -3580,6 +3766,9 @@
       <c r="F76" t="s">
         <v>120</v>
       </c>
+      <c r="H76">
+        <v>46</v>
+      </c>
       <c r="AD76">
         <v>7</v>
       </c>
@@ -3600,6 +3789,9 @@
       <c r="F77" t="s">
         <v>120</v>
       </c>
+      <c r="H77">
+        <v>76</v>
+      </c>
       <c r="AD77">
         <v>7</v>
       </c>
@@ -3640,6 +3832,9 @@
       <c r="F79" t="s">
         <v>120</v>
       </c>
+      <c r="H79">
+        <v>39</v>
+      </c>
       <c r="AD79">
         <v>7</v>
       </c>
@@ -3660,6 +3855,9 @@
       <c r="F80" t="s">
         <v>120</v>
       </c>
+      <c r="H80">
+        <v>57.2</v>
+      </c>
       <c r="AD80">
         <v>7</v>
       </c>
@@ -3680,6 +3878,9 @@
       <c r="F81" t="s">
         <v>120</v>
       </c>
+      <c r="H81">
+        <v>41.1</v>
+      </c>
       <c r="AD81">
         <v>7</v>
       </c>
@@ -3700,6 +3901,9 @@
       <c r="F82" t="s">
         <v>120</v>
       </c>
+      <c r="H82">
+        <v>67.2</v>
+      </c>
       <c r="AD82">
         <v>7</v>
       </c>
@@ -3740,6 +3944,9 @@
       <c r="F84" t="s">
         <v>120</v>
       </c>
+      <c r="H84">
+        <v>51.1</v>
+      </c>
       <c r="AD84">
         <v>7</v>
       </c>
@@ -3760,6 +3967,9 @@
       <c r="F85" t="s">
         <v>120</v>
       </c>
+      <c r="H85">
+        <v>60</v>
+      </c>
       <c r="AD85">
         <v>7</v>
       </c>
@@ -3799,6 +4009,9 @@
       </c>
       <c r="F87" t="s">
         <v>120</v>
+      </c>
+      <c r="H87">
+        <v>21</v>
       </c>
       <c r="AD87">
         <v>7</v>
